--- a/task130/target/moveon_plan_2026-27.xlsx
+++ b/task130/target/moveon_plan_2026-27.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -550,34 +550,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
         <v>22</v>
       </c>
-      <c r="G5" t="n">
-        <v>13</v>
-      </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
         <v>16</v>
@@ -586,7 +586,7 @@
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -596,31 +596,31 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" t="n">
         <v>28</v>
       </c>
-      <c r="C6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" t="n">
-        <v>23</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>17</v>
-      </c>
-      <c r="I6" t="n">
-        <v>21</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
       </c>
       <c r="K6" t="n">
         <v>21</v>
@@ -629,10 +629,10 @@
         <v>21</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -645,19 +645,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
         <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -669,13 +669,13 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
         <v>56</v>
@@ -684,26 +684,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -728,49 +728,95 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5 or more</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="I9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="K9" s="4" t="n">
+      <c r="D10" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>281</v>
+      <c r="M10" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -897,43 +943,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="n">
         <v>13</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I5" t="n">
-        <v>17</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L5" t="n">
-        <v>12</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -943,28 +989,28 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" t="n">
         <v>28</v>
-      </c>
-      <c r="C6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" t="n">
-        <v>23</v>
       </c>
       <c r="H6" t="n">
         <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
         <v>18</v>
@@ -973,13 +1019,13 @@
         <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -992,19 +1038,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
         <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14</v>
       </c>
       <c r="H7" t="n">
         <v>8</v>
@@ -1031,26 +1077,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -1075,49 +1121,95 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5 or more</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="I10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="M9" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="N9" s="4" t="n">
-        <v>264</v>
+      <c r="L10" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1246,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>October 2026 includes lets already offered and accepted whose tenancies start in October.</t>
+          <t>October 2026 is the round of 21 September 2026: every October let has been offered and accepted.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1260,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Four-bedroom column includes homes with four or more bedrooms.</t>
+          <t>No homes with five or more bedrooms are expected to be let before April 2027.</t>
         </is>
       </c>
     </row>
